--- a/output/yearly_benthic_cover_iteration_18_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_18_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.49679533022868</v>
+        <v>45.73674000388186</v>
       </c>
       <c r="M2" t="n">
-        <v>98.60825377644755</v>
+        <v>99.12609423241136</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.97342527709557</v>
+        <v>87.97514333557801</v>
       </c>
       <c r="C3" t="n">
-        <v>45.90554689338353</v>
+        <v>45.90398482370299</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228609871480566</v>
+        <v>2.228615468540721</v>
       </c>
       <c r="E3" t="n">
-        <v>5.690177179348018</v>
+        <v>5.689388213077572</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428699571601889</v>
+        <v>0.742871822846907</v>
       </c>
       <c r="G3" t="n">
-        <v>33.9656575596398</v>
+        <v>33.96509559793604</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17201802936869</v>
+        <v>34.17210385095772</v>
       </c>
       <c r="I3" t="n">
-        <v>6.531155447847126</v>
+        <v>6.534119489425873</v>
       </c>
       <c r="J3" t="n">
-        <v>4.64293723225118</v>
+        <v>4.642948892793168</v>
       </c>
       <c r="K3" t="n">
-        <v>12.02657472290444</v>
+        <v>12.02485666442201</v>
       </c>
       <c r="L3" t="n">
-        <v>48.83343069391487</v>
+        <v>48.83660501149194</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7655523102028</v>
+        <v>106.7654464996169</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.89619969758854</v>
+        <v>87.03503658788965</v>
       </c>
       <c r="C4" t="n">
-        <v>42.45719391143366</v>
+        <v>42.5933809504665</v>
       </c>
       <c r="D4" t="n">
-        <v>2.175834963891256</v>
+        <v>2.183144776341072</v>
       </c>
       <c r="E4" t="n">
-        <v>6.464432873032745</v>
+        <v>6.482720075671372</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444241581984029</v>
+        <v>0.7444242490577446</v>
       </c>
       <c r="G4" t="n">
-        <v>33.16132905788669</v>
+        <v>33.27210193022329</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24351127712653</v>
+        <v>34.24351545665625</v>
       </c>
       <c r="I4" t="n">
-        <v>5.454016378712906</v>
+        <v>5.456478543329011</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652650988740017</v>
+        <v>4.652651556610903</v>
       </c>
       <c r="K4" t="n">
-        <v>13.10380030241145</v>
+        <v>12.96496341211036</v>
       </c>
       <c r="L4" t="n">
-        <v>44.25758480149247</v>
+        <v>44.26015231827245</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81857901533758</v>
+        <v>99.81849668084929</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.66499622160597</v>
+        <v>85.77732403108745</v>
       </c>
       <c r="C5" t="n">
-        <v>42.07231985184777</v>
+        <v>42.18252271662031</v>
       </c>
       <c r="D5" t="n">
-        <v>2.115490293128853</v>
+        <v>2.121421191463787</v>
       </c>
       <c r="E5" t="n">
-        <v>7.043992409853561</v>
+        <v>7.058621244953353</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457430213514331</v>
+        <v>0.7457419778874552</v>
       </c>
       <c r="G5" t="n">
-        <v>32.2416317843108</v>
+        <v>32.33140691549425</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30417898216592</v>
+        <v>34.30413098282293</v>
       </c>
       <c r="I5" t="n">
-        <v>4.553065847348945</v>
+        <v>4.555114356669079</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660893883446456</v>
+        <v>4.660887361796593</v>
       </c>
       <c r="K5" t="n">
-        <v>14.33500377839402</v>
+        <v>14.22267596891255</v>
       </c>
       <c r="L5" t="n">
-        <v>43.44117591479397</v>
+        <v>43.44323246604133</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84849954503576</v>
+        <v>99.84843115157419</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.21705029575003</v>
+        <v>84.29399155071592</v>
       </c>
       <c r="C6" t="n">
-        <v>41.33128183936493</v>
+        <v>41.40651362118692</v>
       </c>
       <c r="D6" t="n">
-        <v>2.044574452796019</v>
+        <v>2.048691474512532</v>
       </c>
       <c r="E6" t="n">
-        <v>7.441183803719184</v>
+        <v>7.45023294835618</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468646350370884</v>
+        <v>0.7468630696192695</v>
       </c>
       <c r="G6" t="n">
-        <v>31.16082209252796</v>
+        <v>31.22297352986505</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35577321170606</v>
+        <v>34.35570120248639</v>
       </c>
       <c r="I6" t="n">
-        <v>3.799928130981907</v>
+        <v>3.80163514075608</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667903968981801</v>
+        <v>4.667894185120432</v>
       </c>
       <c r="K6" t="n">
-        <v>15.78294970424998</v>
+        <v>15.70600844928407</v>
       </c>
       <c r="L6" t="n">
-        <v>42.75929440506982</v>
+        <v>42.76094697517709</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87352594868474</v>
+        <v>99.87346904564808</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.5716988649655</v>
+        <v>82.67268501909085</v>
       </c>
       <c r="C7" t="n">
-        <v>40.27586134926545</v>
+        <v>40.37545937138852</v>
       </c>
       <c r="D7" t="n">
-        <v>1.964322237122781</v>
+        <v>1.969640523328199</v>
       </c>
       <c r="E7" t="n">
-        <v>7.677550946702043</v>
+        <v>7.691437927641578</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478205936328484</v>
+        <v>0.7478182864602541</v>
       </c>
       <c r="G7" t="n">
-        <v>29.93771915699772</v>
+        <v>30.01820170987865</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39974730711101</v>
+        <v>34.39964117717167</v>
       </c>
       <c r="I7" t="n">
-        <v>3.170659913193792</v>
+        <v>3.172081104233904</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673878710205301</v>
+        <v>4.673864290376586</v>
       </c>
       <c r="K7" t="n">
-        <v>17.42830113503449</v>
+        <v>17.32731498090916</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19028395650612</v>
+        <v>42.19162467157022</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89444644080606</v>
+        <v>99.89439902386789</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.60449981513999</v>
+        <v>87.64974275592751</v>
       </c>
       <c r="C8" t="n">
-        <v>42.65121135801944</v>
+        <v>42.68801372601225</v>
       </c>
       <c r="D8" t="n">
-        <v>1.968584284754037</v>
+        <v>1.973918132355745</v>
       </c>
       <c r="E8" t="n">
-        <v>9.563566204821308</v>
+        <v>9.53595096558519</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494431619311973</v>
+        <v>0.7494423768540288</v>
       </c>
       <c r="G8" t="n">
-        <v>30.46215929205484</v>
+        <v>30.52141086008256</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47438544883506</v>
+        <v>34.47434933528531</v>
       </c>
       <c r="I8" t="n">
-        <v>5.702341660673565</v>
+        <v>5.710656230426994</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684019762069981</v>
+        <v>4.684014855337677</v>
       </c>
       <c r="K8" t="n">
-        <v>12.39550018486002</v>
+        <v>12.35025724407251</v>
       </c>
       <c r="L8" t="n">
-        <v>44.76362192680426</v>
+        <v>44.77178633435501</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81033346968371</v>
+        <v>99.81005730443977</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.49270828067991</v>
+        <v>85.60275690598576</v>
       </c>
       <c r="C9" t="n">
-        <v>41.42395330641706</v>
+        <v>41.52688318360623</v>
       </c>
       <c r="D9" t="n">
-        <v>1.87305932615962</v>
+        <v>1.881271542849459</v>
       </c>
       <c r="E9" t="n">
-        <v>9.892959039991867</v>
+        <v>9.882996719627915</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508342856478719</v>
+        <v>0.7508337369485759</v>
       </c>
       <c r="G9" t="n">
-        <v>28.9839922013155</v>
+        <v>29.08887696885572</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53837713980209</v>
+        <v>34.53835189963448</v>
       </c>
       <c r="I9" t="n">
-        <v>4.760772002463745</v>
+        <v>4.767715182141022</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692714285299198</v>
+        <v>4.692710855928597</v>
       </c>
       <c r="K9" t="n">
-        <v>14.50729171932011</v>
+        <v>14.39724309401422</v>
       </c>
       <c r="L9" t="n">
-        <v>43.91035659479968</v>
+        <v>43.91724438264549</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84160162053685</v>
+        <v>99.84137066026594</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.25810098956312</v>
+        <v>83.30113964129171</v>
       </c>
       <c r="C10" t="n">
-        <v>39.92745589567362</v>
+        <v>39.96454436777384</v>
       </c>
       <c r="D10" t="n">
-        <v>1.773162836910712</v>
+        <v>1.77810989030397</v>
       </c>
       <c r="E10" t="n">
-        <v>10.02760485678776</v>
+        <v>10.0042885314493</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520287765348517</v>
+        <v>0.7520293527648891</v>
       </c>
       <c r="G10" t="n">
-        <v>27.4381794099686</v>
+        <v>27.49375550422424</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59332372060317</v>
+        <v>34.59335022718489</v>
       </c>
       <c r="I10" t="n">
-        <v>3.973621535415222</v>
+        <v>3.979422680583871</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700179853342822</v>
+        <v>4.700183454780555</v>
       </c>
       <c r="K10" t="n">
-        <v>16.74189901043687</v>
+        <v>16.69886035870831</v>
       </c>
       <c r="L10" t="n">
-        <v>43.19840142715441</v>
+        <v>43.20415874068059</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86775633326491</v>
+        <v>99.86756346716273</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.96377055417854</v>
+        <v>80.87929690522037</v>
       </c>
       <c r="C11" t="n">
-        <v>38.24853732473612</v>
+        <v>38.15903813719663</v>
       </c>
       <c r="D11" t="n">
-        <v>1.671763811661324</v>
+        <v>1.670751688401821</v>
       </c>
       <c r="E11" t="n">
-        <v>10.00681757124017</v>
+        <v>9.953706519964379</v>
       </c>
       <c r="F11" t="n">
-        <v>0.753055421339859</v>
+        <v>0.7530585745276993</v>
       </c>
       <c r="G11" t="n">
-        <v>25.86911615820548</v>
+        <v>25.83374552926919</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64054938163351</v>
+        <v>34.64069442827415</v>
       </c>
       <c r="I11" t="n">
-        <v>3.315871826724097</v>
+        <v>3.320724073985017</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706596383374118</v>
+        <v>4.706616090798118</v>
       </c>
       <c r="K11" t="n">
-        <v>19.03622944582145</v>
+        <v>19.12070309477961</v>
       </c>
       <c r="L11" t="n">
-        <v>42.60485485345868</v>
+        <v>42.60971924911867</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88962162401626</v>
+        <v>99.88946048109491</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.40254828738497</v>
+        <v>78.4805230135878</v>
       </c>
       <c r="C12" t="n">
-        <v>36.20006844936495</v>
+        <v>36.27370009747285</v>
       </c>
       <c r="D12" t="n">
-        <v>1.559560801706018</v>
+        <v>1.565599088976486</v>
       </c>
       <c r="E12" t="n">
-        <v>9.796273987454972</v>
+        <v>9.789001512914393</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539411536864067</v>
+        <v>0.7539447258885632</v>
       </c>
       <c r="G12" t="n">
-        <v>24.13287047709479</v>
+        <v>24.20783934934261</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68129306957469</v>
+        <v>34.68145739087389</v>
       </c>
       <c r="I12" t="n">
-        <v>2.766476587328053</v>
+        <v>2.770526408788334</v>
       </c>
       <c r="J12" t="n">
-        <v>4.71213221054004</v>
+        <v>4.712154536803517</v>
       </c>
       <c r="K12" t="n">
-        <v>21.59745171261502</v>
+        <v>21.51947698641221</v>
       </c>
       <c r="L12" t="n">
-        <v>42.11037228727771</v>
+        <v>42.11458058072645</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90789244925767</v>
+        <v>99.90775766461151</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.92011751384838</v>
+        <v>76.0598031314193</v>
       </c>
       <c r="C13" t="n">
-        <v>34.14444850575672</v>
+        <v>34.28046012950752</v>
       </c>
       <c r="D13" t="n">
-        <v>1.451939363834014</v>
+        <v>1.46050721214904</v>
       </c>
       <c r="E13" t="n">
-        <v>9.50487949734937</v>
+        <v>9.517093370043867</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7547050684323439</v>
+        <v>0.754708357249314</v>
       </c>
       <c r="G13" t="n">
-        <v>22.4675207081838</v>
+        <v>22.58287208341063</v>
       </c>
       <c r="H13" t="n">
-        <v>34.7164331478878</v>
+        <v>34.71658443346842</v>
       </c>
       <c r="I13" t="n">
-        <v>2.307733050458916</v>
+        <v>2.311110442289833</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716906677702148</v>
+        <v>4.716927232808209</v>
       </c>
       <c r="K13" t="n">
-        <v>24.07988248615161</v>
+        <v>23.94019686858068</v>
       </c>
       <c r="L13" t="n">
-        <v>41.69882243622144</v>
+        <v>41.70238393500102</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92315342812977</v>
+        <v>99.92304093308921</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.05355218566663</v>
+        <v>82.99740603446075</v>
       </c>
       <c r="C14" t="n">
-        <v>38.51773790573305</v>
+        <v>38.70772734064087</v>
       </c>
       <c r="D14" t="n">
-        <v>1.45374078346698</v>
+        <v>1.462151384227809</v>
       </c>
       <c r="E14" t="n">
-        <v>11.946321467203</v>
+        <v>11.96013958916478</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556414302124828</v>
+        <v>0.7555579733267155</v>
       </c>
       <c r="G14" t="n">
-        <v>24.40982314152932</v>
+        <v>24.57345377923749</v>
       </c>
       <c r="H14" t="n">
-        <v>36.67393279394136</v>
+        <v>36.72082570652421</v>
       </c>
       <c r="I14" t="n">
-        <v>3.091333630485471</v>
+        <v>2.803040268687784</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722758938828015</v>
+        <v>4.722237333291969</v>
       </c>
       <c r="K14" t="n">
-        <v>16.94644781433336</v>
+        <v>17.00259396553924</v>
       </c>
       <c r="L14" t="n">
-        <v>44.43289751430633</v>
+        <v>44.1963490843936</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89708323437273</v>
+        <v>99.90667039057371</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.26855653882792</v>
+        <v>82.22795145378032</v>
       </c>
       <c r="C15" t="n">
-        <v>38.20988306869606</v>
+        <v>38.36530480489552</v>
       </c>
       <c r="D15" t="n">
-        <v>1.425046161095494</v>
+        <v>1.433222502202504</v>
       </c>
       <c r="E15" t="n">
-        <v>12.14031984115726</v>
+        <v>12.1190466303187</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7564309787019333</v>
+        <v>0.7562740946239136</v>
       </c>
       <c r="G15" t="n">
-        <v>23.92801052048521</v>
+        <v>24.09312438883068</v>
       </c>
       <c r="H15" t="n">
-        <v>36.71225235541846</v>
+        <v>36.76148991052682</v>
       </c>
       <c r="I15" t="n">
-        <v>2.578803065082496</v>
+        <v>2.338080835878229</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727693616887081</v>
+        <v>4.726713091399457</v>
       </c>
       <c r="K15" t="n">
-        <v>17.73144346117207</v>
+        <v>17.77204854621971</v>
       </c>
       <c r="L15" t="n">
-        <v>43.97280309150727</v>
+        <v>43.78478441919899</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91412962137539</v>
+        <v>99.92213777031421</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.72210916102961</v>
+        <v>79.7743774088037</v>
       </c>
       <c r="C16" t="n">
-        <v>36.06152721601413</v>
+        <v>36.27282702042675</v>
       </c>
       <c r="D16" t="n">
-        <v>1.329455498882291</v>
+        <v>1.340902541814648</v>
       </c>
       <c r="E16" t="n">
-        <v>11.68444861402058</v>
+        <v>11.66340530472608</v>
       </c>
       <c r="F16" t="n">
-        <v>0.757111272652965</v>
+        <v>0.7568903014974162</v>
       </c>
       <c r="G16" t="n">
-        <v>22.32294365771121</v>
+        <v>22.54118371961959</v>
       </c>
       <c r="H16" t="n">
-        <v>36.74526941039021</v>
+        <v>36.79144291688271</v>
       </c>
       <c r="I16" t="n">
-        <v>2.150935253291323</v>
+        <v>1.949988239904432</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731945454081029</v>
+        <v>4.730564384358848</v>
       </c>
       <c r="K16" t="n">
-        <v>20.2778908389704</v>
+        <v>20.2256225911963</v>
       </c>
       <c r="L16" t="n">
-        <v>43.58894852654095</v>
+        <v>43.43660369849147</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92836658152547</v>
+        <v>99.93505331011451</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.54180798328217</v>
+        <v>81.64410609406471</v>
       </c>
       <c r="C17" t="n">
-        <v>37.376481063494</v>
+        <v>37.63867517134008</v>
       </c>
       <c r="D17" t="n">
-        <v>1.330627471670293</v>
+        <v>1.341949451835138</v>
       </c>
       <c r="E17" t="n">
-        <v>12.51628188968749</v>
+        <v>12.50053896360545</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7577786991368033</v>
+        <v>0.7574812438040638</v>
       </c>
       <c r="G17" t="n">
-        <v>22.80474199509016</v>
+        <v>23.06809191786771</v>
       </c>
       <c r="H17" t="n">
-        <v>37.23978165457991</v>
+        <v>37.32947700883525</v>
       </c>
       <c r="I17" t="n">
-        <v>2.156479403512507</v>
+        <v>1.912309734341705</v>
       </c>
       <c r="J17" t="n">
-        <v>4.736116869605018</v>
+        <v>4.734257773775395</v>
       </c>
       <c r="K17" t="n">
-        <v>18.45819201671781</v>
+        <v>18.35589390593529</v>
       </c>
       <c r="L17" t="n">
-        <v>44.09350758486877</v>
+        <v>43.94173699396528</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92818066508059</v>
+        <v>99.93630607124065</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.09772743860566</v>
+        <v>79.26627388447076</v>
       </c>
       <c r="C18" t="n">
-        <v>35.26486053917386</v>
+        <v>35.55582794173255</v>
       </c>
       <c r="D18" t="n">
-        <v>1.242837067098227</v>
+        <v>1.256341082696267</v>
       </c>
       <c r="E18" t="n">
-        <v>11.99023698632917</v>
+        <v>11.96885583676337</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7583530142238071</v>
+        <v>0.7579892047367076</v>
       </c>
       <c r="G18" t="n">
-        <v>21.30016045853325</v>
+        <v>21.59648527461179</v>
       </c>
       <c r="H18" t="n">
-        <v>37.26800542025888</v>
+        <v>37.35450986095088</v>
       </c>
       <c r="I18" t="n">
-        <v>1.79842815326355</v>
+        <v>1.594660095107336</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739706338898792</v>
+        <v>4.737432529604419</v>
       </c>
       <c r="K18" t="n">
-        <v>20.90227256139433</v>
+        <v>20.73372611552924</v>
       </c>
       <c r="L18" t="n">
-        <v>43.77296469377868</v>
+        <v>43.6573262278954</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94009779434687</v>
+        <v>99.94688028515718</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.17519875587904</v>
+        <v>78.33416334415067</v>
       </c>
       <c r="C19" t="n">
-        <v>34.61884053141107</v>
+        <v>34.86270942726826</v>
       </c>
       <c r="D19" t="n">
-        <v>1.210409123320963</v>
+        <v>1.223140754347071</v>
       </c>
       <c r="E19" t="n">
-        <v>11.92733068404784</v>
+        <v>11.87519271660465</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7588379348207714</v>
+        <v>0.7584200509067309</v>
       </c>
       <c r="G19" t="n">
-        <v>20.74439943073519</v>
+        <v>21.02577210429431</v>
       </c>
       <c r="H19" t="n">
-        <v>37.2918360414829</v>
+        <v>37.37574241598745</v>
       </c>
       <c r="I19" t="n">
-        <v>1.499648448841539</v>
+        <v>1.335769983843394</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742737092629818</v>
+        <v>4.740125318167065</v>
       </c>
       <c r="K19" t="n">
-        <v>21.82480124412097</v>
+        <v>21.66583665584933</v>
       </c>
       <c r="L19" t="n">
-        <v>43.5064018868773</v>
+        <v>43.42695354506542</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95004366240934</v>
+        <v>99.95549962818301</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.66428082749738</v>
+        <v>75.8084897477742</v>
       </c>
       <c r="C20" t="n">
-        <v>32.33834375132668</v>
+        <v>32.54237563864343</v>
       </c>
       <c r="D20" t="n">
-        <v>1.121326170964495</v>
+        <v>1.133165414413145</v>
       </c>
       <c r="E20" t="n">
-        <v>11.25790951636045</v>
+        <v>11.18725726053428</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7592559424930182</v>
+        <v>0.7587914439460243</v>
       </c>
       <c r="G20" t="n">
-        <v>19.2176657746954</v>
+        <v>19.47909729541917</v>
       </c>
       <c r="H20" t="n">
-        <v>37.31237833762047</v>
+        <v>37.39404505784815</v>
       </c>
       <c r="I20" t="n">
-        <v>1.250395444782185</v>
+        <v>1.113686750950776</v>
       </c>
       <c r="J20" t="n">
-        <v>4.74534964058136</v>
+        <v>4.742446524662649</v>
       </c>
       <c r="K20" t="n">
-        <v>24.33571917250261</v>
+        <v>24.1915102522258</v>
       </c>
       <c r="L20" t="n">
-        <v>43.284280174814</v>
+        <v>43.22900938735734</v>
       </c>
       <c r="M20" t="n">
-        <v>99.9583430986433</v>
+        <v>99.96289527822658</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.72830077718092</v>
+        <v>81.83630284212511</v>
       </c>
       <c r="C21" t="n">
-        <v>36.07362340031504</v>
+        <v>36.37910576529102</v>
       </c>
       <c r="D21" t="n">
-        <v>1.122163589726913</v>
+        <v>1.133851027667514</v>
       </c>
       <c r="E21" t="n">
-        <v>13.27902716065998</v>
+        <v>13.22936518043637</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7598229632120423</v>
+        <v>0.7592505450310506</v>
       </c>
       <c r="G21" t="n">
-        <v>20.93954986687603</v>
+        <v>21.27864991786988</v>
       </c>
       <c r="H21" t="n">
-        <v>39.04777576088451</v>
+        <v>39.20443698538267</v>
       </c>
       <c r="I21" t="n">
-        <v>1.831067915746187</v>
+        <v>1.485433279293565</v>
       </c>
       <c r="J21" t="n">
-        <v>4.748893520075261</v>
+        <v>4.745315906444064</v>
       </c>
       <c r="K21" t="n">
-        <v>18.27169922281909</v>
+        <v>18.16369715787489</v>
       </c>
       <c r="L21" t="n">
-        <v>45.59368732771628</v>
+        <v>45.40771257441885</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93900995085042</v>
+        <v>99.95051549758476</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_18_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_18_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.73674000388186</v>
+        <v>45.32584353811136</v>
       </c>
       <c r="M2" t="n">
-        <v>99.12609423241136</v>
+        <v>98.95429355191015</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.97514333557801</v>
+        <v>87.92562398137578</v>
       </c>
       <c r="C3" t="n">
-        <v>45.90398482370299</v>
+        <v>45.86206978723941</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228615468540721</v>
+        <v>2.228520068747263</v>
       </c>
       <c r="E3" t="n">
-        <v>5.689388213077572</v>
+        <v>5.662818240209427</v>
       </c>
       <c r="F3" t="n">
-        <v>0.742871822846907</v>
+        <v>0.7428400229157543</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96509559793604</v>
+        <v>33.95104788277362</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17210385095772</v>
+        <v>34.1706410541247</v>
       </c>
       <c r="I3" t="n">
-        <v>6.534119489425873</v>
+        <v>6.527006569381558</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642948892793168</v>
+        <v>4.642750143223465</v>
       </c>
       <c r="K3" t="n">
-        <v>12.02485666442201</v>
+        <v>12.07437601862422</v>
       </c>
       <c r="L3" t="n">
-        <v>48.83660501149194</v>
+        <v>48.82924599432552</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7654464996169</v>
+        <v>106.7656918001891</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.03503658788965</v>
+        <v>87.02015805006846</v>
       </c>
       <c r="C4" t="n">
-        <v>42.5933809504665</v>
+        <v>42.58628897353062</v>
       </c>
       <c r="D4" t="n">
-        <v>2.183144776341072</v>
+        <v>2.184847180517805</v>
       </c>
       <c r="E4" t="n">
-        <v>6.482720075671372</v>
+        <v>6.460263894400018</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444242490577446</v>
+        <v>0.7443909549584217</v>
       </c>
       <c r="G4" t="n">
-        <v>33.27210193022329</v>
+        <v>33.28570035449631</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24351545665625</v>
+        <v>34.2419839280874</v>
       </c>
       <c r="I4" t="n">
-        <v>5.456478543329011</v>
+        <v>5.450528269118371</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652651556610903</v>
+        <v>4.652443468490135</v>
       </c>
       <c r="K4" t="n">
-        <v>12.96496341211036</v>
+        <v>12.97984194993154</v>
       </c>
       <c r="L4" t="n">
-        <v>44.26015231827245</v>
+        <v>44.25256333849946</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81849668084929</v>
+        <v>99.81869426196162</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.77732403108745</v>
+        <v>85.83241643496169</v>
       </c>
       <c r="C5" t="n">
-        <v>42.18252271662031</v>
+        <v>42.2444785844211</v>
       </c>
       <c r="D5" t="n">
-        <v>2.121421191463787</v>
+        <v>2.126710104058704</v>
       </c>
       <c r="E5" t="n">
-        <v>7.058621244953353</v>
+        <v>7.046716831250309</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457419778874552</v>
+        <v>0.7457063390685192</v>
       </c>
       <c r="G5" t="n">
-        <v>32.33140691549425</v>
+        <v>32.39999387407994</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30413098282293</v>
+        <v>34.30249159715189</v>
       </c>
       <c r="I5" t="n">
-        <v>4.555114356669079</v>
+        <v>4.550133070174079</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660887361796593</v>
+        <v>4.660664619178245</v>
       </c>
       <c r="K5" t="n">
-        <v>14.22267596891255</v>
+        <v>14.16758356503831</v>
       </c>
       <c r="L5" t="n">
-        <v>43.44323246604133</v>
+        <v>43.43653428750951</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84843115157419</v>
+        <v>99.84859643696893</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.29399155071592</v>
+        <v>84.35638198110043</v>
       </c>
       <c r="C6" t="n">
-        <v>41.40651362118692</v>
+        <v>41.47505562100928</v>
       </c>
       <c r="D6" t="n">
-        <v>2.048691474512532</v>
+        <v>2.054280752294341</v>
       </c>
       <c r="E6" t="n">
-        <v>7.45023294835618</v>
+        <v>7.439638071289538</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468630696192695</v>
+        <v>0.7468253200007571</v>
       </c>
       <c r="G6" t="n">
-        <v>31.22297352986505</v>
+        <v>31.29654749979959</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35570120248639</v>
+        <v>34.35396472003482</v>
       </c>
       <c r="I6" t="n">
-        <v>3.80163514075608</v>
+        <v>3.797467367676648</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667894185120432</v>
+        <v>4.667658250004732</v>
       </c>
       <c r="K6" t="n">
-        <v>15.70600844928407</v>
+        <v>15.64361801889956</v>
       </c>
       <c r="L6" t="n">
-        <v>42.76094697517709</v>
+        <v>42.75493377480853</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87346904564808</v>
+        <v>99.87360741471737</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.67268501909085</v>
+        <v>82.73318371857397</v>
       </c>
       <c r="C7" t="n">
-        <v>40.37545937138852</v>
+        <v>40.4415194041462</v>
       </c>
       <c r="D7" t="n">
-        <v>1.969640523328199</v>
+        <v>1.97505178857581</v>
       </c>
       <c r="E7" t="n">
-        <v>7.691437927641578</v>
+        <v>7.680807404999313</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478182864602541</v>
+        <v>0.7477787414700788</v>
       </c>
       <c r="G7" t="n">
-        <v>30.01820170987865</v>
+        <v>30.08951042679604</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39964117717167</v>
+        <v>34.39782210762363</v>
       </c>
       <c r="I7" t="n">
-        <v>3.172081104233904</v>
+        <v>3.168596114921111</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673864290376586</v>
+        <v>4.673617134187992</v>
       </c>
       <c r="K7" t="n">
-        <v>17.32731498090916</v>
+        <v>17.26681628142602</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19162467157022</v>
+        <v>42.1861791097701</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89439902386789</v>
+        <v>99.89451479534233</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.64974275592751</v>
+        <v>87.5817885242724</v>
       </c>
       <c r="C8" t="n">
-        <v>42.68801372601225</v>
+        <v>42.72573878462839</v>
       </c>
       <c r="D8" t="n">
-        <v>1.973918132355745</v>
+        <v>1.979268786561975</v>
       </c>
       <c r="E8" t="n">
-        <v>9.53595096558519</v>
+        <v>9.500443074571461</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494423768540288</v>
+        <v>0.7493753484376106</v>
       </c>
       <c r="G8" t="n">
-        <v>30.52141086008256</v>
+        <v>30.58787670416756</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47434933528531</v>
+        <v>34.47126602813009</v>
       </c>
       <c r="I8" t="n">
-        <v>5.710656230426994</v>
+        <v>5.609962654668631</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684014855337677</v>
+        <v>4.683595927735066</v>
       </c>
       <c r="K8" t="n">
-        <v>12.35025724407251</v>
+        <v>12.4182114757276</v>
       </c>
       <c r="L8" t="n">
-        <v>44.77178633435501</v>
+        <v>44.66944940100424</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81005730443977</v>
+        <v>99.81339966136024</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.60275690598576</v>
+        <v>85.42392972663932</v>
       </c>
       <c r="C9" t="n">
-        <v>41.52688318360623</v>
+        <v>41.43826659592064</v>
       </c>
       <c r="D9" t="n">
-        <v>1.881271542849459</v>
+        <v>1.88117378794164</v>
       </c>
       <c r="E9" t="n">
-        <v>9.882996719627915</v>
+        <v>9.810174857292342</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508337369485759</v>
+        <v>0.7507448744925346</v>
       </c>
       <c r="G9" t="n">
-        <v>29.08887696885572</v>
+        <v>29.07190386436632</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53835189963448</v>
+        <v>34.5342642266566</v>
       </c>
       <c r="I9" t="n">
-        <v>4.767715182141022</v>
+        <v>4.683512650311547</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692710855928597</v>
+        <v>4.692155465578342</v>
       </c>
       <c r="K9" t="n">
-        <v>14.39724309401422</v>
+        <v>14.57607027336066</v>
       </c>
       <c r="L9" t="n">
-        <v>43.91724438264549</v>
+        <v>43.82983083475568</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84137066026594</v>
+        <v>99.84416770403698</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.30113964129171</v>
+        <v>83.03341532803526</v>
       </c>
       <c r="C10" t="n">
-        <v>39.96454436777384</v>
+        <v>39.77397085358758</v>
       </c>
       <c r="D10" t="n">
-        <v>1.77810989030397</v>
+        <v>1.773633445499474</v>
       </c>
       <c r="E10" t="n">
-        <v>10.0042885314493</v>
+        <v>9.900869001612717</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520293527648891</v>
+        <v>0.7519229948527872</v>
       </c>
       <c r="G10" t="n">
-        <v>27.49375550422424</v>
+        <v>27.40996145529174</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59335022718489</v>
+        <v>34.58845776322821</v>
       </c>
       <c r="I10" t="n">
-        <v>3.979422680583871</v>
+        <v>3.909051949720407</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700183454780555</v>
+        <v>4.69951871782992</v>
       </c>
       <c r="K10" t="n">
-        <v>16.69886035870831</v>
+        <v>16.96658467196474</v>
       </c>
       <c r="L10" t="n">
-        <v>43.20415874068059</v>
+        <v>43.1293469008279</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86756346716273</v>
+        <v>99.86990242638022</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.87929690522037</v>
+        <v>80.52101240709175</v>
       </c>
       <c r="C11" t="n">
-        <v>38.15903813719663</v>
+        <v>37.86690785821882</v>
       </c>
       <c r="D11" t="n">
-        <v>1.670751688401821</v>
+        <v>1.661862923505496</v>
       </c>
       <c r="E11" t="n">
-        <v>9.953706519964379</v>
+        <v>9.820594790204773</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530585745276993</v>
+        <v>0.7529383527104914</v>
       </c>
       <c r="G11" t="n">
-        <v>25.83374552926919</v>
+        <v>25.6826453024155</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64069442827415</v>
+        <v>34.6351642246826</v>
       </c>
       <c r="I11" t="n">
-        <v>3.320724073985017</v>
+        <v>3.261942109132306</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706616090798118</v>
+        <v>4.705864704440571</v>
       </c>
       <c r="K11" t="n">
-        <v>19.12070309477961</v>
+        <v>19.47898759290825</v>
       </c>
       <c r="L11" t="n">
-        <v>42.60971924911867</v>
+        <v>42.5455197724918</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88946048109491</v>
+        <v>99.89141522361888</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.4805230135878</v>
+        <v>77.903483869884</v>
       </c>
       <c r="C12" t="n">
-        <v>36.27370009747285</v>
+        <v>35.75356034678578</v>
       </c>
       <c r="D12" t="n">
-        <v>1.565599088976486</v>
+        <v>1.546617219836946</v>
       </c>
       <c r="E12" t="n">
-        <v>9.789001512914393</v>
+        <v>9.593138143205477</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539447258885632</v>
+        <v>0.7538151146924582</v>
       </c>
       <c r="G12" t="n">
-        <v>24.20783934934261</v>
+        <v>23.90162324091883</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68145739087389</v>
+        <v>34.67549527585308</v>
       </c>
       <c r="I12" t="n">
-        <v>2.770526408788334</v>
+        <v>2.721450408549348</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712154536803517</v>
+        <v>4.711344466827864</v>
       </c>
       <c r="K12" t="n">
-        <v>21.51947698641221</v>
+        <v>22.09651613011599</v>
       </c>
       <c r="L12" t="n">
-        <v>42.11458058072645</v>
+        <v>42.05931402006676</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90775766461151</v>
+        <v>99.90939049696854</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.0598031314193</v>
+        <v>75.35993007781771</v>
       </c>
       <c r="C13" t="n">
-        <v>34.28046012950752</v>
+        <v>33.62961914999704</v>
       </c>
       <c r="D13" t="n">
-        <v>1.46050721214904</v>
+        <v>1.435792972004372</v>
       </c>
       <c r="E13" t="n">
-        <v>9.517093370043867</v>
+        <v>9.284091968626658</v>
       </c>
       <c r="F13" t="n">
-        <v>0.754708357249314</v>
+        <v>0.7545720489326244</v>
       </c>
       <c r="G13" t="n">
-        <v>22.58287208341063</v>
+        <v>22.1889309317438</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71658443346842</v>
+        <v>34.71031425090073</v>
       </c>
       <c r="I13" t="n">
-        <v>2.311110442289833</v>
+        <v>2.270152599780618</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716927232808209</v>
+        <v>4.716075305828903</v>
       </c>
       <c r="K13" t="n">
-        <v>23.94019686858068</v>
+        <v>24.64006992218229</v>
       </c>
       <c r="L13" t="n">
-        <v>41.70238393500102</v>
+        <v>41.65471508313874</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92304093308921</v>
+        <v>99.92440415531807</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.99740603446075</v>
+        <v>82.73517140517939</v>
       </c>
       <c r="C14" t="n">
-        <v>38.70772734064087</v>
+        <v>38.21429097196256</v>
       </c>
       <c r="D14" t="n">
-        <v>1.462151384227809</v>
+        <v>1.437511582500713</v>
       </c>
       <c r="E14" t="n">
-        <v>11.96013958916478</v>
+        <v>11.82096014320945</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555579733267155</v>
+        <v>0.7554752539690242</v>
       </c>
       <c r="G14" t="n">
-        <v>24.57345377923749</v>
+        <v>24.24608560187141</v>
       </c>
       <c r="H14" t="n">
-        <v>36.72082570652421</v>
+        <v>36.7824567230448</v>
       </c>
       <c r="I14" t="n">
-        <v>2.803040268687784</v>
+        <v>2.970961763277584</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722237333291969</v>
+        <v>4.721720337306401</v>
       </c>
       <c r="K14" t="n">
-        <v>17.00259396553924</v>
+        <v>17.2648285948206</v>
       </c>
       <c r="L14" t="n">
-        <v>44.1963490843936</v>
+        <v>44.42196677177264</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90667039057371</v>
+        <v>99.9010863385558</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.22795145378032</v>
+        <v>81.82976440241482</v>
       </c>
       <c r="C15" t="n">
-        <v>38.36530480489552</v>
+        <v>37.7588030367931</v>
       </c>
       <c r="D15" t="n">
-        <v>1.433222502202504</v>
+        <v>1.403251111092748</v>
       </c>
       <c r="E15" t="n">
-        <v>12.1190466303187</v>
+        <v>11.96074388300162</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562740946239136</v>
+        <v>0.7562379328463368</v>
       </c>
       <c r="G15" t="n">
-        <v>24.09312438883068</v>
+        <v>23.6766889514127</v>
       </c>
       <c r="H15" t="n">
-        <v>36.76148991052682</v>
+        <v>36.8280545655908</v>
       </c>
       <c r="I15" t="n">
-        <v>2.338080835878229</v>
+        <v>2.478300878181013</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726713091399457</v>
+        <v>4.726487080289605</v>
       </c>
       <c r="K15" t="n">
-        <v>17.77204854621971</v>
+        <v>18.17023559758518</v>
       </c>
       <c r="L15" t="n">
-        <v>43.78478441919899</v>
+        <v>43.9884346499751</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92213777031421</v>
+        <v>99.91747328435339</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.7743774088037</v>
+        <v>79.22968414753348</v>
       </c>
       <c r="C16" t="n">
-        <v>36.27282702042675</v>
+        <v>35.54105007877498</v>
       </c>
       <c r="D16" t="n">
-        <v>1.340902541814648</v>
+        <v>1.305884208133564</v>
       </c>
       <c r="E16" t="n">
-        <v>11.66340530472608</v>
+        <v>11.47533564845182</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568903014974162</v>
+        <v>0.7568955900481272</v>
       </c>
       <c r="G16" t="n">
-        <v>22.54118371961959</v>
+        <v>22.03384266588097</v>
       </c>
       <c r="H16" t="n">
-        <v>36.79144291688271</v>
+        <v>36.86008183407472</v>
       </c>
       <c r="I16" t="n">
-        <v>1.949988239904432</v>
+        <v>2.067046763143486</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730564384358848</v>
+        <v>4.730597437800795</v>
       </c>
       <c r="K16" t="n">
-        <v>20.2256225911963</v>
+        <v>20.77031585246652</v>
       </c>
       <c r="L16" t="n">
-        <v>43.43660369849147</v>
+        <v>43.61979237769792</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93505331011451</v>
+        <v>99.93115830893942</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.64410609406471</v>
+        <v>81.05812052435387</v>
       </c>
       <c r="C17" t="n">
-        <v>37.63867517134008</v>
+        <v>36.85077320143546</v>
       </c>
       <c r="D17" t="n">
-        <v>1.341949451835138</v>
+        <v>1.307002870540498</v>
       </c>
       <c r="E17" t="n">
-        <v>12.50053896360545</v>
+        <v>12.29871355322574</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574812438040638</v>
+        <v>0.7575439711505922</v>
       </c>
       <c r="G17" t="n">
-        <v>23.06809191786771</v>
+        <v>22.5190803638795</v>
       </c>
       <c r="H17" t="n">
-        <v>37.32947700883525</v>
+        <v>37.35802016532264</v>
       </c>
       <c r="I17" t="n">
-        <v>1.912309734341705</v>
+        <v>2.083109780543694</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734257773775395</v>
+        <v>4.734649819691202</v>
       </c>
       <c r="K17" t="n">
-        <v>18.35589390593529</v>
+        <v>18.94187947564613</v>
       </c>
       <c r="L17" t="n">
-        <v>43.94173699396528</v>
+        <v>44.13796976128394</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93630607124065</v>
+        <v>99.93062243836553</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.26627388447076</v>
+        <v>78.58083727231973</v>
       </c>
       <c r="C18" t="n">
-        <v>35.55582794173255</v>
+        <v>34.69437830961548</v>
       </c>
       <c r="D18" t="n">
-        <v>1.256341082696267</v>
+        <v>1.218271324978299</v>
       </c>
       <c r="E18" t="n">
-        <v>11.96885583676337</v>
+        <v>11.75329616985984</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579892047367076</v>
+        <v>0.7581022109146879</v>
       </c>
       <c r="G18" t="n">
-        <v>21.59648527461179</v>
+        <v>20.99027514824897</v>
       </c>
       <c r="H18" t="n">
-        <v>37.35450986095088</v>
+        <v>37.38554956712422</v>
       </c>
       <c r="I18" t="n">
-        <v>1.594660095107336</v>
+        <v>1.737204032976912</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737432529604419</v>
+        <v>4.7381388182168</v>
       </c>
       <c r="K18" t="n">
-        <v>20.73372611552924</v>
+        <v>21.41916272768028</v>
       </c>
       <c r="L18" t="n">
-        <v>43.6573262278954</v>
+        <v>43.82859480213359</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94688028515718</v>
+        <v>99.94213583942934</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.33416334415067</v>
+        <v>77.63030914506797</v>
       </c>
       <c r="C19" t="n">
-        <v>34.86270942726826</v>
+        <v>34.00240175093187</v>
       </c>
       <c r="D19" t="n">
-        <v>1.223140754347071</v>
+        <v>1.184569142499622</v>
       </c>
       <c r="E19" t="n">
-        <v>11.87519271660465</v>
+        <v>11.67092142484877</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584200509067309</v>
+        <v>0.7585763626769054</v>
       </c>
       <c r="G19" t="n">
-        <v>21.02577210429431</v>
+        <v>20.40960147661303</v>
       </c>
       <c r="H19" t="n">
-        <v>37.37574241598745</v>
+        <v>37.40893219805908</v>
       </c>
       <c r="I19" t="n">
-        <v>1.335769983843394</v>
+        <v>1.456606273639895</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740125318167065</v>
+        <v>4.741102266730659</v>
       </c>
       <c r="K19" t="n">
-        <v>21.66583665584933</v>
+        <v>22.36969085493204</v>
       </c>
       <c r="L19" t="n">
-        <v>43.42695354506542</v>
+        <v>43.57938420030401</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95549962818301</v>
+        <v>99.9514768061679</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.8084897477742</v>
+        <v>75.05153281536879</v>
       </c>
       <c r="C20" t="n">
-        <v>32.54237563864343</v>
+        <v>31.64719850383358</v>
       </c>
       <c r="D20" t="n">
-        <v>1.133165414413145</v>
+        <v>1.09332840623854</v>
       </c>
       <c r="E20" t="n">
-        <v>11.18725726053428</v>
+        <v>10.9743911697622</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587914439460243</v>
+        <v>0.7589855419362589</v>
       </c>
       <c r="G20" t="n">
-        <v>19.47909729541917</v>
+        <v>18.83756401699127</v>
       </c>
       <c r="H20" t="n">
-        <v>37.39404505784815</v>
+        <v>37.42911073238091</v>
       </c>
       <c r="I20" t="n">
-        <v>1.113686750950776</v>
+        <v>1.214493310957987</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742446524662649</v>
+        <v>4.743659637101619</v>
       </c>
       <c r="K20" t="n">
-        <v>24.1915102522258</v>
+        <v>24.94846718463122</v>
       </c>
       <c r="L20" t="n">
-        <v>43.22900938735734</v>
+        <v>43.36387302615632</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96289527822658</v>
+        <v>99.95953871462112</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.83630284212511</v>
+        <v>81.44514510432205</v>
       </c>
       <c r="C21" t="n">
-        <v>36.37910576529102</v>
+        <v>35.66101704351137</v>
       </c>
       <c r="D21" t="n">
-        <v>1.133851027667514</v>
+        <v>1.09408868429101</v>
       </c>
       <c r="E21" t="n">
-        <v>13.22936518043637</v>
+        <v>13.1233743082858</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7592505450310506</v>
+        <v>0.7595133248479473</v>
       </c>
       <c r="G21" t="n">
-        <v>21.27864991786988</v>
+        <v>20.70883866276532</v>
       </c>
       <c r="H21" t="n">
-        <v>39.20443698538267</v>
+        <v>39.31331355677772</v>
       </c>
       <c r="I21" t="n">
-        <v>1.485433279293565</v>
+        <v>1.699058287054573</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745315906444064</v>
+        <v>4.746958280299671</v>
       </c>
       <c r="K21" t="n">
-        <v>18.16369715787489</v>
+        <v>18.55485489567795</v>
       </c>
       <c r="L21" t="n">
-        <v>45.40771257441885</v>
+        <v>45.72753214021292</v>
       </c>
       <c r="M21" t="n">
-        <v>99.95051549758476</v>
+        <v>99.94340407940223</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_18_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_18_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.32584353811136</v>
+        <v>44.0657914121244</v>
       </c>
       <c r="M2" t="n">
-        <v>98.95429355191015</v>
+        <v>93.72900829905532</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.92562398137578</v>
+        <v>81.44220536491184</v>
       </c>
       <c r="C3" t="n">
-        <v>45.86206978723941</v>
+        <v>43.1977609204674</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228520068747263</v>
+        <v>2.178402848262648</v>
       </c>
       <c r="E3" t="n">
-        <v>5.662818240209427</v>
+        <v>4.145972700976114</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428400229157543</v>
+        <v>0.7376084813884893</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95104788277362</v>
+        <v>32.76680950928399</v>
       </c>
       <c r="H3" t="n">
-        <v>34.1706410541247</v>
+        <v>33.9299901438705</v>
       </c>
       <c r="I3" t="n">
-        <v>6.527006569381558</v>
+        <v>3.073368672452039</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642750143223465</v>
+        <v>4.610053008678058</v>
       </c>
       <c r="K3" t="n">
-        <v>12.07437601862422</v>
+        <v>18.55779463508815</v>
       </c>
       <c r="L3" t="n">
-        <v>48.82924599432552</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7656918001891</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.02015805006846</v>
+        <v>88.47226975499963</v>
       </c>
       <c r="C4" t="n">
-        <v>42.58628897353062</v>
+        <v>42.69220280464495</v>
       </c>
       <c r="D4" t="n">
-        <v>2.184847180517805</v>
+        <v>2.184168617989306</v>
       </c>
       <c r="E4" t="n">
-        <v>6.460263894400018</v>
+        <v>6.461217127218696</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7443909549584217</v>
+        <v>0.7395607743977956</v>
       </c>
       <c r="G4" t="n">
-        <v>33.28570035449631</v>
+        <v>33.42025347960841</v>
       </c>
       <c r="H4" t="n">
-        <v>34.2419839280874</v>
+        <v>34.01979562229859</v>
       </c>
       <c r="I4" t="n">
-        <v>5.450528269118371</v>
+        <v>7.025019293500602</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652443468490135</v>
+        <v>4.622254839986222</v>
       </c>
       <c r="K4" t="n">
-        <v>12.97984194993154</v>
+        <v>11.52773024500039</v>
       </c>
       <c r="L4" t="n">
-        <v>44.25256333849946</v>
+        <v>45.54651779558672</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81869426196162</v>
+        <v>99.76645084523204</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.83241643496169</v>
+        <v>87.36978849300739</v>
       </c>
       <c r="C5" t="n">
-        <v>42.2444785844211</v>
+        <v>42.67841586131931</v>
       </c>
       <c r="D5" t="n">
-        <v>2.126710104058704</v>
+        <v>2.131685725061395</v>
       </c>
       <c r="E5" t="n">
-        <v>7.046716831250309</v>
+        <v>7.28384321518342</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457063390685192</v>
+        <v>0.7412162724775425</v>
       </c>
       <c r="G5" t="n">
-        <v>32.39999387407994</v>
+        <v>32.61720577965171</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30249159715189</v>
+        <v>34.09594853396695</v>
       </c>
       <c r="I5" t="n">
-        <v>4.550133070174079</v>
+        <v>5.867287263681725</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660664619178245</v>
+        <v>4.63260170298464</v>
       </c>
       <c r="K5" t="n">
-        <v>14.16758356503831</v>
+        <v>12.6302115069926</v>
       </c>
       <c r="L5" t="n">
-        <v>43.43653428750951</v>
+        <v>44.49623320686865</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84859643696893</v>
+        <v>99.80486057518057</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.35638198110043</v>
+        <v>86.12610453173728</v>
       </c>
       <c r="C6" t="n">
-        <v>41.47505562100928</v>
+        <v>42.34516803994862</v>
       </c>
       <c r="D6" t="n">
-        <v>2.054280752294341</v>
+        <v>2.072534371247866</v>
       </c>
       <c r="E6" t="n">
-        <v>7.439638071289538</v>
+        <v>7.89817256610593</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468253200007571</v>
+        <v>0.7426215678130066</v>
       </c>
       <c r="G6" t="n">
-        <v>31.29654749979959</v>
+        <v>31.71212307595001</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35396472003482</v>
+        <v>34.1605921193983</v>
       </c>
       <c r="I6" t="n">
-        <v>3.797467367676648</v>
+        <v>4.898676032390873</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667658250004732</v>
+        <v>4.641384798831291</v>
       </c>
       <c r="K6" t="n">
-        <v>15.64361801889956</v>
+        <v>13.87389546826273</v>
       </c>
       <c r="L6" t="n">
-        <v>42.75493377480853</v>
+        <v>43.61795629001969</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87360741471737</v>
+        <v>99.83701979823104</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.73318371857397</v>
+        <v>84.74943195802392</v>
       </c>
       <c r="C7" t="n">
-        <v>40.4415194041462</v>
+        <v>41.72915067856885</v>
       </c>
       <c r="D7" t="n">
-        <v>1.97505178857581</v>
+        <v>2.007307042548273</v>
       </c>
       <c r="E7" t="n">
-        <v>7.680807404999313</v>
+        <v>8.331065108808152</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7477787414700788</v>
+        <v>0.7438158442046442</v>
       </c>
       <c r="G7" t="n">
-        <v>30.08951042679604</v>
+        <v>30.71407107530141</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39782210762363</v>
+        <v>34.21552883341363</v>
       </c>
       <c r="I7" t="n">
-        <v>3.168596114921111</v>
+        <v>4.088795027468787</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673617134187992</v>
+        <v>4.648849026279026</v>
       </c>
       <c r="K7" t="n">
-        <v>17.26681628142602</v>
+        <v>15.25056804197609</v>
       </c>
       <c r="L7" t="n">
-        <v>42.1861791097701</v>
+        <v>42.88420694522198</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89451479534233</v>
+        <v>99.86392566576691</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.5817885242724</v>
+        <v>83.18079286193583</v>
       </c>
       <c r="C8" t="n">
-        <v>42.72573878462839</v>
+        <v>40.79550817303397</v>
       </c>
       <c r="D8" t="n">
-        <v>1.979268786561975</v>
+        <v>1.933246320901512</v>
       </c>
       <c r="E8" t="n">
-        <v>9.500443074571461</v>
+        <v>8.592350449381419</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7493753484376106</v>
+        <v>0.7448328621423994</v>
       </c>
       <c r="G8" t="n">
-        <v>30.58787670416756</v>
+        <v>29.58085815852761</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47126602813009</v>
+        <v>34.26231165855037</v>
       </c>
       <c r="I8" t="n">
-        <v>5.609962654668631</v>
+        <v>3.411988024042519</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683595927735066</v>
+        <v>4.655205388389996</v>
       </c>
       <c r="K8" t="n">
-        <v>12.4182114757276</v>
+        <v>16.81920713806417</v>
       </c>
       <c r="L8" t="n">
-        <v>44.66944940100424</v>
+        <v>42.27170704924998</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81339966136024</v>
+        <v>99.88642236034812</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.42392972663932</v>
+        <v>81.48193971017108</v>
       </c>
       <c r="C9" t="n">
-        <v>41.43826659592064</v>
+        <v>39.62632186474963</v>
       </c>
       <c r="D9" t="n">
-        <v>1.88117378794164</v>
+        <v>1.853512672106655</v>
       </c>
       <c r="E9" t="n">
-        <v>9.810174857292342</v>
+        <v>8.712411793474557</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507448744925346</v>
+        <v>0.7457002391800658</v>
       </c>
       <c r="G9" t="n">
-        <v>29.07190386436632</v>
+        <v>28.36084303165921</v>
       </c>
       <c r="H9" t="n">
-        <v>34.5342642266566</v>
+        <v>34.30221100228302</v>
       </c>
       <c r="I9" t="n">
-        <v>4.683512650311547</v>
+        <v>2.846634476592141</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692155465578342</v>
+        <v>4.660626494875411</v>
       </c>
       <c r="K9" t="n">
-        <v>14.57607027336066</v>
+        <v>18.51806028982893</v>
       </c>
       <c r="L9" t="n">
-        <v>43.82983083475568</v>
+        <v>41.76084040030913</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84416770403698</v>
+        <v>99.90522255488769</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.03341532803526</v>
+        <v>85.96380581022771</v>
       </c>
       <c r="C10" t="n">
-        <v>39.77397085358758</v>
+        <v>42.72570197821425</v>
       </c>
       <c r="D10" t="n">
-        <v>1.773633445499474</v>
+        <v>1.855594485973621</v>
       </c>
       <c r="E10" t="n">
-        <v>9.900869001612717</v>
+        <v>10.49190949453365</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519229948527872</v>
+        <v>0.7465377889426795</v>
       </c>
       <c r="G10" t="n">
-        <v>27.40996145529174</v>
+        <v>29.6796485285598</v>
       </c>
       <c r="H10" t="n">
-        <v>34.58845776322821</v>
+        <v>35.62768967839416</v>
       </c>
       <c r="I10" t="n">
-        <v>3.909051949720407</v>
+        <v>2.896564652932049</v>
       </c>
       <c r="J10" t="n">
-        <v>4.69951871782992</v>
+        <v>4.665861180891747</v>
       </c>
       <c r="K10" t="n">
-        <v>16.96658467196474</v>
+        <v>14.03619418977228</v>
       </c>
       <c r="L10" t="n">
-        <v>43.1293469008279</v>
+        <v>43.14165999994476</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86990242638022</v>
+        <v>99.9035561679313</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.52101240709175</v>
+        <v>85.83003286804704</v>
       </c>
       <c r="C11" t="n">
-        <v>37.86690785821882</v>
+        <v>42.97494428605152</v>
       </c>
       <c r="D11" t="n">
-        <v>1.661862923505496</v>
+        <v>1.84728781742746</v>
       </c>
       <c r="E11" t="n">
-        <v>9.820594790204773</v>
+        <v>10.86596805786405</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529383527104914</v>
+        <v>0.747254683927248</v>
       </c>
       <c r="G11" t="n">
-        <v>25.6826453024155</v>
+        <v>29.55570226337184</v>
       </c>
       <c r="H11" t="n">
-        <v>34.6351642246826</v>
+        <v>35.67081897623837</v>
       </c>
       <c r="I11" t="n">
-        <v>3.261942109132306</v>
+        <v>2.472659294672768</v>
       </c>
       <c r="J11" t="n">
-        <v>4.705864704440571</v>
+        <v>4.6703417745453</v>
       </c>
       <c r="K11" t="n">
-        <v>19.47898759290825</v>
+        <v>14.16996713195296</v>
       </c>
       <c r="L11" t="n">
-        <v>42.5455197724918</v>
+        <v>42.77274567881681</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89141522361888</v>
+        <v>99.91765709682129</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.903483869884</v>
+        <v>84.18652830627563</v>
       </c>
       <c r="C12" t="n">
-        <v>35.75356034678578</v>
+        <v>41.71613316285706</v>
       </c>
       <c r="D12" t="n">
-        <v>1.546617219836946</v>
+        <v>1.776911166950034</v>
       </c>
       <c r="E12" t="n">
-        <v>9.593138143205477</v>
+        <v>10.79570949558985</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538151146924582</v>
+        <v>0.7478648419067648</v>
       </c>
       <c r="G12" t="n">
-        <v>23.90162324091883</v>
+        <v>28.4297102505512</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67549527585308</v>
+        <v>35.69994537089657</v>
       </c>
       <c r="I12" t="n">
-        <v>2.721450408549348</v>
+        <v>2.062231918463937</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711344466827864</v>
+        <v>4.674155261917281</v>
       </c>
       <c r="K12" t="n">
-        <v>22.09651613011599</v>
+        <v>15.81347169372437</v>
       </c>
       <c r="L12" t="n">
-        <v>42.05931402006676</v>
+        <v>42.40171016301098</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90939049696854</v>
+        <v>99.93131501959242</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.35993007781771</v>
+        <v>85.36105198972834</v>
       </c>
       <c r="C13" t="n">
-        <v>33.62961914999704</v>
+        <v>42.69882722520693</v>
       </c>
       <c r="D13" t="n">
-        <v>1.435792972004372</v>
+        <v>1.778236962089458</v>
       </c>
       <c r="E13" t="n">
-        <v>9.284091968626658</v>
+        <v>11.43765877353697</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545720489326244</v>
+        <v>0.7484228414234474</v>
       </c>
       <c r="G13" t="n">
-        <v>22.1889309317438</v>
+        <v>28.76636724561944</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71031425090073</v>
+        <v>36.04202685907641</v>
       </c>
       <c r="I13" t="n">
-        <v>2.270152599780618</v>
+        <v>1.910696549086055</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716075305828903</v>
+        <v>4.677642758896547</v>
       </c>
       <c r="K13" t="n">
-        <v>24.64006992218229</v>
+        <v>14.63894801027166</v>
       </c>
       <c r="L13" t="n">
-        <v>41.65471508313874</v>
+        <v>42.59858236464061</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92440415531807</v>
+        <v>99.93635760011921</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.73517140517939</v>
+        <v>83.67754120900887</v>
       </c>
       <c r="C14" t="n">
-        <v>38.21429097196256</v>
+        <v>41.31254956265624</v>
       </c>
       <c r="D14" t="n">
-        <v>1.437511582500713</v>
+        <v>1.708012082703106</v>
       </c>
       <c r="E14" t="n">
-        <v>11.82096014320945</v>
+        <v>11.25151377265484</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554752539690242</v>
+        <v>0.7488978515768263</v>
       </c>
       <c r="G14" t="n">
-        <v>24.24608560187141</v>
+        <v>27.63034616784731</v>
       </c>
       <c r="H14" t="n">
-        <v>36.7824567230448</v>
+        <v>36.06490206779379</v>
       </c>
       <c r="I14" t="n">
-        <v>2.970961763277584</v>
+        <v>1.593257694077834</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721720337306401</v>
+        <v>4.680611572355166</v>
       </c>
       <c r="K14" t="n">
-        <v>17.2648285948206</v>
+        <v>16.32245879099113</v>
       </c>
       <c r="L14" t="n">
-        <v>44.42196677177264</v>
+        <v>42.31191674221133</v>
       </c>
       <c r="M14" t="n">
-        <v>99.9010863385558</v>
+        <v>99.9469250958587</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.82976440241482</v>
+        <v>82.98631228540275</v>
       </c>
       <c r="C15" t="n">
-        <v>37.7588030367931</v>
+        <v>40.84575594367803</v>
       </c>
       <c r="D15" t="n">
-        <v>1.403251111092748</v>
+        <v>1.678708259834219</v>
       </c>
       <c r="E15" t="n">
-        <v>11.96074388300162</v>
+        <v>11.28360408005646</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562379328463368</v>
+        <v>0.7493041802752335</v>
       </c>
       <c r="G15" t="n">
-        <v>23.6766889514127</v>
+        <v>27.15630106119488</v>
       </c>
       <c r="H15" t="n">
-        <v>36.8280545655908</v>
+        <v>36.08446976275317</v>
       </c>
       <c r="I15" t="n">
-        <v>2.478300878181013</v>
+        <v>1.350773814568579</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726487080289605</v>
+        <v>4.683151126720211</v>
       </c>
       <c r="K15" t="n">
-        <v>18.17023559758518</v>
+        <v>17.01368771459722</v>
       </c>
       <c r="L15" t="n">
-        <v>43.9884346499751</v>
+        <v>42.09555496425457</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91747328435339</v>
+        <v>99.95499862252983</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.22968414753348</v>
+        <v>80.88093469869142</v>
       </c>
       <c r="C16" t="n">
-        <v>35.54105007877498</v>
+        <v>38.95014746889507</v>
       </c>
       <c r="D16" t="n">
-        <v>1.305884208133564</v>
+        <v>1.591349870763132</v>
       </c>
       <c r="E16" t="n">
-        <v>11.47533564845182</v>
+        <v>10.88411055048074</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568955900481272</v>
+        <v>0.7496519515014403</v>
       </c>
       <c r="G16" t="n">
-        <v>22.03384266588097</v>
+        <v>25.74311285535993</v>
       </c>
       <c r="H16" t="n">
-        <v>36.86008183407472</v>
+        <v>36.10121748767818</v>
       </c>
       <c r="I16" t="n">
-        <v>2.067046763143486</v>
+        <v>1.126167286023981</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730597437800795</v>
+        <v>4.685324696884003</v>
       </c>
       <c r="K16" t="n">
-        <v>20.77031585246652</v>
+        <v>19.11906530130859</v>
       </c>
       <c r="L16" t="n">
-        <v>43.61979237769792</v>
+        <v>41.89326573494719</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93115830893942</v>
+        <v>99.96247850515086</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.05812052435387</v>
+        <v>84.97877906864875</v>
       </c>
       <c r="C17" t="n">
-        <v>36.85077320143546</v>
+        <v>41.65484580381113</v>
       </c>
       <c r="D17" t="n">
-        <v>1.307002870540498</v>
+        <v>1.592134850080451</v>
       </c>
       <c r="E17" t="n">
-        <v>12.29871355322574</v>
+        <v>12.33824796419222</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575439711505922</v>
+        <v>0.750021738993134</v>
       </c>
       <c r="G17" t="n">
-        <v>22.5190803638795</v>
+        <v>26.99498870715612</v>
       </c>
       <c r="H17" t="n">
-        <v>37.35802016532264</v>
+        <v>37.35820277395664</v>
       </c>
       <c r="I17" t="n">
-        <v>2.083109780543694</v>
+        <v>1.257547165563076</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734649819691202</v>
+        <v>4.68763586870709</v>
       </c>
       <c r="K17" t="n">
-        <v>18.94187947564613</v>
+        <v>15.02122093135128</v>
       </c>
       <c r="L17" t="n">
-        <v>44.13796976128394</v>
+        <v>43.28203569317365</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93062243836553</v>
+        <v>99.95810242833605</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.58083727231973</v>
+        <v>86.48342523513145</v>
       </c>
       <c r="C18" t="n">
-        <v>34.69437830961548</v>
+        <v>42.39081449610246</v>
       </c>
       <c r="D18" t="n">
-        <v>1.218271324978299</v>
+        <v>1.593351278183452</v>
       </c>
       <c r="E18" t="n">
-        <v>11.75329616985984</v>
+        <v>12.93511214724673</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581022109146879</v>
+        <v>0.7505947730681851</v>
       </c>
       <c r="G18" t="n">
-        <v>20.99027514824897</v>
+        <v>27.14414386707382</v>
       </c>
       <c r="H18" t="n">
-        <v>37.38554956712422</v>
+        <v>37.38674531087149</v>
       </c>
       <c r="I18" t="n">
-        <v>1.737204032976912</v>
+        <v>1.982260527011635</v>
       </c>
       <c r="J18" t="n">
-        <v>4.7381388182168</v>
+        <v>4.691217331676159</v>
       </c>
       <c r="K18" t="n">
-        <v>21.41916272768028</v>
+        <v>13.51657476486854</v>
       </c>
       <c r="L18" t="n">
-        <v>43.82859480213359</v>
+        <v>44.02658583269466</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94213583942934</v>
+        <v>99.93397509366567</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.63030914506797</v>
+        <v>84.02688631208805</v>
       </c>
       <c r="C19" t="n">
-        <v>34.00240175093187</v>
+        <v>40.24197710461371</v>
       </c>
       <c r="D19" t="n">
-        <v>1.184569142499622</v>
+        <v>1.500408780660048</v>
       </c>
       <c r="E19" t="n">
-        <v>11.67092142484877</v>
+        <v>12.45608273562508</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585763626769054</v>
+        <v>0.7510869601191077</v>
       </c>
       <c r="G19" t="n">
-        <v>20.40960147661303</v>
+        <v>25.5607864752144</v>
       </c>
       <c r="H19" t="n">
-        <v>37.40893219805908</v>
+        <v>37.41126089848068</v>
       </c>
       <c r="I19" t="n">
-        <v>1.456606273639895</v>
+        <v>1.652966961244324</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741102266730659</v>
+        <v>4.694293500744426</v>
       </c>
       <c r="K19" t="n">
-        <v>22.36969085493204</v>
+        <v>15.97311368791195</v>
       </c>
       <c r="L19" t="n">
-        <v>43.57938420030401</v>
+        <v>43.72984641505735</v>
       </c>
       <c r="M19" t="n">
-        <v>99.9514768061679</v>
+        <v>99.94493720758301</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.05153281536879</v>
+        <v>81.5214661708502</v>
       </c>
       <c r="C20" t="n">
-        <v>31.64719850383358</v>
+        <v>37.99252355499804</v>
       </c>
       <c r="D20" t="n">
-        <v>1.09332840623854</v>
+        <v>1.406073875638258</v>
       </c>
       <c r="E20" t="n">
-        <v>10.9743911697622</v>
+        <v>11.90264202943915</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589855419362589</v>
+        <v>0.7515102370420854</v>
       </c>
       <c r="G20" t="n">
-        <v>18.83756401699127</v>
+        <v>23.95370819394704</v>
       </c>
       <c r="H20" t="n">
-        <v>37.42911073238091</v>
+        <v>37.43234410753455</v>
       </c>
       <c r="I20" t="n">
-        <v>1.214493310957987</v>
+        <v>1.378248745736075</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743659637101619</v>
+        <v>4.696938981513036</v>
       </c>
       <c r="K20" t="n">
-        <v>24.94846718463122</v>
+        <v>18.4785338291498</v>
       </c>
       <c r="L20" t="n">
-        <v>43.36387302615632</v>
+        <v>43.48302686692871</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95953871462112</v>
+        <v>99.95408425107655</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.44514510432205</v>
+        <v>79.01851021634999</v>
       </c>
       <c r="C21" t="n">
-        <v>35.66101704351137</v>
+        <v>35.70240181847412</v>
       </c>
       <c r="D21" t="n">
-        <v>1.09408868429101</v>
+        <v>1.31226221918219</v>
       </c>
       <c r="E21" t="n">
-        <v>13.1233743082858</v>
+        <v>11.30002746127969</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7595133248479473</v>
+        <v>0.7518745223337076</v>
       </c>
       <c r="G21" t="n">
-        <v>20.70883866276532</v>
+        <v>22.35554391334022</v>
       </c>
       <c r="H21" t="n">
-        <v>39.31331355677772</v>
+        <v>37.45048897332238</v>
       </c>
       <c r="I21" t="n">
-        <v>1.699058287054573</v>
+        <v>1.149097362306136</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746958280299671</v>
+        <v>4.699215764585674</v>
       </c>
       <c r="K21" t="n">
-        <v>18.55485489567795</v>
+        <v>20.98148978365001</v>
       </c>
       <c r="L21" t="n">
-        <v>45.72753214021292</v>
+        <v>43.27782371049431</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94340407940223</v>
+        <v>99.96171531261844</v>
       </c>
     </row>
   </sheetData>
